--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486532_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486532_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9611</v>
+        <v>6.1192</v>
       </c>
       <c r="E2" t="n">
-        <v>4.883</v>
+        <v>5.4418</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0781</v>
+        <v>0.6774</v>
       </c>
       <c r="G2" t="n">
         <v>4.9508</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5123</v>
+        <v>-0.3542</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8784</v>
+        <v>-0.3196</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3661</v>
+        <v>-0.0346</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7658</v>
+        <v>4.1048</v>
       </c>
       <c r="E3" t="n">
         <v>4.5828</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8171</v>
+        <v>-0.478</v>
       </c>
       <c r="G3" t="n">
         <v>4.515</v>
@@ -688,13 +688,13 @@
         <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8819</v>
+        <v>-0.5429</v>
       </c>
       <c r="T3" t="n">
         <v>-0.4759</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4061</v>
+        <v>-0.067</v>
       </c>
       <c r="V3" t="n">
         <v>-2.2599</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0507</v>
+        <v>2.9969</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.7876</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4867</v>
+        <v>2.2093</v>
       </c>
       <c r="G4" t="n">
         <v>0.3332</v>
@@ -766,13 +766,13 @@
         <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1525</v>
+        <v>-0.2064</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8904</v>
+        <v>-0.6669</v>
       </c>
       <c r="U4" t="n">
-        <v>0.738</v>
+        <v>0.4605</v>
       </c>
       <c r="V4" t="n">
         <v>1.13</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1544</v>
+        <v>2.1659</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3567</v>
+        <v>4.2449</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.2023</v>
+        <v>-2.079</v>
       </c>
       <c r="G5" t="n">
         <v>2.1869</v>
@@ -844,13 +844,13 @@
         <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1627</v>
+        <v>0.1742</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1406</v>
+        <v>0.0288</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0221</v>
+        <v>0.1454</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1952</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6757</v>
+        <v>1.6372</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3968</v>
+        <v>-0.6203</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0725</v>
+        <v>2.2575</v>
       </c>
       <c r="G6" t="n">
         <v>0.2919</v>
@@ -922,13 +922,13 @@
         <v>2.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7912</v>
+        <v>-0.8298</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2824</v>
+        <v>-0.5059</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5088</v>
+        <v>-0.3239</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ PÉREZ</t>
+          <t>L. GIOVANNETTI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4918</v>
+        <v>0.7453</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8473000000000001</v>
+        <v>4.0037</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6445</v>
+        <v>-3.2584</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1442</v>
+        <v>2.4191</v>
       </c>
       <c r="H7" t="n">
-        <v>0.067</v>
+        <v>1.8613</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2112</v>
+        <v>0.5578</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3587</v>
+        <v>3.9364</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1674</v>
+        <v>2.0622</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1912</v>
+        <v>1.8742</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5029</v>
+        <v>-1.5173</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1004</v>
+        <v>-0.2009</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4024</v>
+        <v>-1.3164</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>1.723</v>
+        <v>-0.2839</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2281</v>
+        <v>0.0673</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4949</v>
+        <v>-0.3512</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7395</v>
+        <v>-2.2599</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. GIOVANNETTI</t>
+          <t>A. GONZÁLEZ PÉREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0497</v>
+        <v>0.6478</v>
       </c>
       <c r="E8" t="n">
-        <v>4.339</v>
+        <v>0.065</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.2893</v>
+        <v>0.5829</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4191</v>
+        <v>-0.1442</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8613</v>
+        <v>0.067</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5578</v>
+        <v>-0.2112</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9364</v>
+        <v>0.3587</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0622</v>
+        <v>0.1674</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8742</v>
+        <v>0.1912</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5173</v>
+        <v>-0.5029</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2009</v>
+        <v>-0.1004</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3164</v>
+        <v>-0.4024</v>
       </c>
       <c r="P8" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0205</v>
+        <v>0.879</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4026</v>
+        <v>0.4458</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.382</v>
+        <v>0.4332</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.2599</v>
+        <v>-0.7395</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2929</v>
+        <v>-0.4278</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2331</v>
+        <v>-2.1214</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9402</v>
+        <v>1.6936</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4605</v>
@@ -1156,13 +1156,13 @@
         <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.442</v>
+        <v>-0.5768</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4795</v>
+        <v>-0.3677</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0375</v>
+        <v>-0.2091</v>
       </c>
       <c r="V9" t="n">
         <v>0.7395</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6287</v>
+        <v>-0.5593</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5284</v>
+        <v>-2.3049</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8997</v>
+        <v>1.7456</v>
       </c>
       <c r="G10" t="n">
         <v>0.0016</v>
@@ -1234,13 +1234,13 @@
         <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1953</v>
+        <v>-0.1259</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.822</v>
+        <v>-0.5984</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6267</v>
+        <v>0.4726</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0107</v>
+        <v>-0.7333</v>
       </c>
       <c r="E11" t="n">
         <v>-3.9494</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9388</v>
+        <v>3.2162</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1675</v>
@@ -1312,13 +1312,13 @@
         <v>2.3926</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.798</v>
+        <v>-0.5206</v>
       </c>
       <c r="T11" t="n">
         <v>-0.5444</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2537</v>
+        <v>0.0237</v>
       </c>
       <c r="V11" t="n">
         <v>2.8249</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7869</v>
+        <v>-1.3785</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7386</v>
+        <v>-0.5151</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0483</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-1.15</v>
@@ -1390,13 +1390,13 @@
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7467</v>
+        <v>-0.3383</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.274</v>
+        <v>-0.0505</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4728</v>
+        <v>-0.2878</v>
       </c>
       <c r="V12" t="n">
         <v>-0.7602</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.1856</v>
+        <v>-2.0738</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0556</v>
+        <v>-0.9439</v>
       </c>
       <c r="F13" t="n">
         <v>-1.13</v>
@@ -1468,10 +1468,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3665</v>
+        <v>-0.2548</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0433</v>
       </c>
       <c r="U13" t="n">
         <v>-0.298</v>
@@ -1504,10 +1504,10 @@
         <v>13.2444</v>
       </c>
       <c r="E14" t="n">
-        <v>8.670900000000003</v>
+        <v>8.6708</v>
       </c>
       <c r="F14" t="n">
-        <v>4.573499999999999</v>
+        <v>4.5737</v>
       </c>
       <c r="G14" t="n">
         <v>10.1323</v>
@@ -1528,7 +1528,7 @@
         <v>9.960700000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.077199999999999</v>
+        <v>-5.0772</v>
       </c>
       <c r="N14" t="n">
         <v>-3.8337</v>
@@ -1546,13 +1546,13 @@
         <v>16.313</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.9802</v>
+        <v>-2.980399999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.944199999999999</v>
+        <v>-2.9441</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.03610000000000008</v>
+        <v>-0.03620000000000012</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5203</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1451</v>
+        <v>3.9833</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4528</v>
+        <v>3.2293</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6923</v>
+        <v>0.754</v>
       </c>
       <c r="G15" t="n">
         <v>3.813</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0154</v>
+        <v>-0.1772</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1454</v>
+        <v>-0.3689</v>
       </c>
       <c r="U15" t="n">
-        <v>0.13</v>
+        <v>0.1917</v>
       </c>
       <c r="V15" t="n">
         <v>0.5649999999999999</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. MC MULLEN</t>
+          <t>P. KRUTOUS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8112</v>
+        <v>1.0415</v>
       </c>
       <c r="E16" t="n">
-        <v>3.866</v>
+        <v>1.0552</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0549</v>
+        <v>-0.0137</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.5167</v>
+        <v>-2.0804</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1763</v>
+        <v>-2.278</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.3403</v>
+        <v>0.1976</v>
       </c>
       <c r="J16" t="n">
-        <v>1.949</v>
+        <v>-1.2276</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5721000000000001</v>
+        <v>-1.3806</v>
       </c>
       <c r="L16" t="n">
-        <v>1.377</v>
+        <v>0.153</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.4657</v>
+        <v>-0.8528</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7484</v>
+        <v>-0.8974</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.7173</v>
+        <v>0.0446</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0.6525</v>
       </c>
       <c r="S16" t="n">
-        <v>4.0026</v>
+        <v>0.2094</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9838</v>
+        <v>0.0228</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0188</v>
+        <v>0.1866</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7602</v>
+        <v>2.2599</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0207</v>
+        <v>2.2599</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GODSPOWER JOHNSON</t>
+          <t>C. DIAZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5171</v>
+        <v>0.4167</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3738</v>
+        <v>0.4686</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1433</v>
+        <v>-0.0519</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.281</v>
+        <v>0.6453</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0914</v>
+        <v>0.4318</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1896</v>
+        <v>0.2136</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7247</v>
+        <v>1.3531</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1095</v>
+        <v>0.1857</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6152</v>
+        <v>1.1674</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0057</v>
+        <v>-0.7077</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2009</v>
+        <v>0.2461</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.9539</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2175</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0157</v>
+        <v>0.4239</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7367</v>
+        <v>0.2031</v>
       </c>
       <c r="U17" t="n">
-        <v>0.279</v>
+        <v>0.2208</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. KRUTOUS</t>
+          <t>N. MC MULLEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3645</v>
+        <v>0.3551</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4964</v>
+        <v>1.6309</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1319</v>
+        <v>-1.2757</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.0804</v>
+        <v>-1.5167</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.278</v>
+        <v>-0.1763</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1976</v>
+        <v>-1.3403</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2276</v>
+        <v>1.949</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3806</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>0.153</v>
+        <v>1.377</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8528</v>
+        <v>-3.4657</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8974</v>
+        <v>-0.7484</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0446</v>
+        <v>-2.7173</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6525</v>
+        <v>-0.435</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
         <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4676</v>
+        <v>1.5466</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.536</v>
+        <v>0.7487</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0684</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>2.2599</v>
+        <v>0.7602</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2599</v>
+        <v>0.0207</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. DIAZ RODRIGUEZ</t>
+          <t>J. GODSPOWER JOHNSON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8035</v>
+        <v>0.2808</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2019</v>
+        <v>-0.0732</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6016</v>
+        <v>0.354</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6453</v>
+        <v>-0.281</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4318</v>
+        <v>-0.0914</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2136</v>
+        <v>-0.1896</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3531</v>
+        <v>0.7247</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1857</v>
+        <v>0.1095</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1674</v>
+        <v>0.6152</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7077</v>
+        <v>-1.0057</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2461</v>
+        <v>-0.2009</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9539</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6525</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7964</v>
+        <v>0.7793</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4675</v>
+        <v>0.2896</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3289</v>
+        <v>0.4897</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8265</v>
+        <v>-0.6839</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8136</v>
+        <v>-0.7018</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0129</v>
+        <v>0.0179</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7785</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0479</v>
+        <v>0.0946</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0433</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. CRUZ UCEDA</t>
+          <t>S. CECCARDI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.926</v>
+        <v>-0.7177</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3141</v>
+        <v>1.1377</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3881</v>
+        <v>-1.8554</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0613</v>
+        <v>-0.2281</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6605</v>
+        <v>0.8333</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4008</v>
+        <v>-1.0614</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3552</v>
+        <v>2.1037</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9942</v>
+        <v>2.0622</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3609</v>
+        <v>0.0415</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7062</v>
+        <v>-2.3318</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6663</v>
+        <v>-1.2289</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0399</v>
+        <v>-1.1029</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3872</v>
+        <v>-0.1421</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9589</v>
+        <v>-0.4434</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5718</v>
+        <v>0.3013</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. CECCARDI</t>
+          <t>I. CRUZ UCEDA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3188</v>
+        <v>-1.0724</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6907</v>
+        <v>-2.0906</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0095</v>
+        <v>1.0182</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2281</v>
+        <v>-2.0613</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8333</v>
+        <v>-1.6605</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0614</v>
+        <v>-0.4008</v>
       </c>
       <c r="J22" t="n">
-        <v>2.1037</v>
+        <v>-1.3552</v>
       </c>
       <c r="K22" t="n">
-        <v>2.0622</v>
+        <v>-0.9942</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0415</v>
+        <v>-0.3609</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.3318</v>
+        <v>-0.7062</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2289</v>
+        <v>-0.6663</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1029</v>
+        <v>-0.0399</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7432</v>
+        <v>-0.5336</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8904</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1472</v>
+        <v>0.2019</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2677</v>
+        <v>-1.7024</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1984</v>
+        <v>0.2487</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0693</v>
+        <v>-1.9511</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4386</v>
@@ -2248,13 +2248,13 @@
         <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5635</v>
+        <v>1.1287</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0036</v>
+        <v>0.4506</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5599</v>
+        <v>0.678</v>
       </c>
       <c r="V23" t="n">
         <v>1.13</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3752</v>
+        <v>-2.7317</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0019</v>
+        <v>-0.6666</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3733</v>
+        <v>-2.0651</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6179</v>
@@ -2326,13 +2326,13 @@
         <v>0.435</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7775</v>
+        <v>-0.134</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.536</v>
+        <v>-0.2007</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2415</v>
+        <v>0.0667</v>
       </c>
       <c r="V24" t="n">
         <v>0.7602</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.2108</v>
+        <v>-4.7059</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.22</v>
+        <v>-2.4377</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.9907</v>
+        <v>-2.2682</v>
       </c>
       <c r="G25" t="n">
         <v>-1.31</v>
@@ -2404,13 +2404,13 @@
         <v>0.435</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.096</v>
+        <v>0.4089</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.0973</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5889</v>
+        <v>0.3115</v>
       </c>
       <c r="V25" t="n">
         <v>-2.0647</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.3539</v>
+        <v>-6.9628</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.7035</v>
+        <v>-6.374</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6504</v>
+        <v>-0.5887</v>
       </c>
       <c r="G26" t="n">
         <v>-2.2782</v>
@@ -2482,13 +2482,13 @@
         <v>0.87</v>
       </c>
       <c r="S26" t="n">
-        <v>0.7297</v>
+        <v>0.1208</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5997</v>
+        <v>-0.0709</v>
       </c>
       <c r="U26" t="n">
-        <v>0.13</v>
+        <v>0.1917</v>
       </c>
       <c r="V26" t="n">
         <v>-1.3252</v>
@@ -2515,25 +2515,25 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-13.2445</v>
+        <v>-12.4994</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.573700000000001</v>
+        <v>-4.573499999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-8.6708</v>
+        <v>-7.925700000000001</v>
       </c>
       <c r="G27" t="n">
         <v>-10.1324</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.4146</v>
+        <v>-1.414599999999999</v>
       </c>
       <c r="I27" t="n">
         <v>-8.717400000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>5.077199999999999</v>
+        <v>5.077200000000001</v>
       </c>
       <c r="K27" t="n">
         <v>3.834</v>
@@ -2560,13 +2560,13 @@
         <v>8.699999999999998</v>
       </c>
       <c r="S27" t="n">
-        <v>2.980300000000001</v>
+        <v>3.7253</v>
       </c>
       <c r="T27" t="n">
-        <v>0.03609999999999991</v>
+        <v>0.03609999999999981</v>
       </c>
       <c r="U27" t="n">
-        <v>2.9441</v>
+        <v>3.6892</v>
       </c>
       <c r="V27" t="n">
         <v>1.5204</v>
